--- a/Data/dim_education.xlsx
+++ b/Data/dim_education.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Machine Learning\Power BI\Projects\4\Dataset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Analysis\Power BI\Projects\4- Siemens\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287FB119-5E0A-4B8B-B2A3-D2E6BC641A30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E117294-DA7B-4365-8F6C-087BE1D3FDFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{56350C31-280B-463A-A3AA-DD87B752F566}"/>
   </bookViews>
@@ -41,15 +41,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="45">
   <si>
-    <t>Education Key</t>
-  </si>
-  <si>
-    <t>Education</t>
-  </si>
-  <si>
-    <t>Education Field</t>
-  </si>
-  <si>
     <t>CC Education</t>
   </si>
   <si>
@@ -174,6 +165,15 @@
   </si>
   <si>
     <t>30</t>
+  </si>
+  <si>
+    <t>education</t>
+  </si>
+  <si>
+    <t>education_field</t>
+  </si>
+  <si>
+    <t>education_key</t>
   </si>
 </sst>
 </file>
@@ -558,436 +558,436 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>2</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2">
-        <v>2</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="2">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="2">
-        <v>2</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="2">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="C6" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>3</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="2">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>2</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="2">
-        <v>3</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="2">
-        <v>3</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="2">
-        <v>2</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="2">
-        <v>3</v>
+      <c r="A10" s="2">
+        <v>3</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2">
+        <v>4</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>4</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <v>4</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="2">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <v>3</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <v>2</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>3</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
         <v>4</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="B17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="2">
+      <c r="C17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <v>5</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <v>5</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <v>1</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
         <v>4</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2">
-        <v>4</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="2">
-        <v>3</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="2">
-        <v>2</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="B21" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <v>3</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <v>2</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <v>1</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <v>5</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="2">
-        <v>3</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B17" s="2">
-        <v>4</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B18" s="2">
-        <v>5</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
+      <c r="D25" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <v>5</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <v>5</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <v>2</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="2">
-        <v>5</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B20" s="2">
+      <c r="C28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
         <v>1</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21" s="2">
-        <v>4</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" s="2">
-        <v>3</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B23" s="2">
-        <v>2</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="2">
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <v>5</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
         <v>1</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="2">
-        <v>5</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="2">
-        <v>5</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="2">
-        <v>5</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+      <c r="B31" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="B28" s="2">
-        <v>2</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B29" s="2">
-        <v>1</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B30" s="2">
-        <v>5</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B31" s="2">
-        <v>1</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
